--- a/data/trans_dic/IMC_inf_MED_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R3-Provincia-trans_dic.xlsx
@@ -532,7 +532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 71,23%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.2819390109274167</v>
+        <v>0.2654524715910742</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.2892254254887906</v>
+        <v>0.2503126008165801</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0.1045216669714024</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.2192529533364676</v>
+        <v>0.1975177763935075</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.2411179909226401</v>
+        <v>0.1667498381256748</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>0.05373134896595479</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.2524908595826965</v>
+        <v>0.2341226701697428</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.264773299366759</v>
+        <v>0.2104235450199991</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>0.08099872088633343</v>
@@ -667,28 +667,28 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.1706312617059764</v>
+        <v>0.1787113984880463</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.1742725774689705</v>
+        <v>0.1592943672843305</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0.02680780150634936</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.105665315260016</v>
+        <v>0.1176405367163436</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.127388745953418</v>
+        <v>0.09077088648635916</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.1781792547232384</v>
+        <v>0.1669615665092532</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.1747673574856408</v>
+        <v>0.1502972685818266</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0.03754084377741491</v>
@@ -702,28 +702,28 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.4216272338941706</v>
+        <v>0.3998608549436372</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.4203538803132207</v>
+        <v>0.3505496511644096</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0.2393085961405794</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.348363049312045</v>
+        <v>0.3055622336187083</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.3890039866318502</v>
+        <v>0.2652460461084846</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0.1876120913713049</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.3424624404288705</v>
+        <v>0.3035177667425268</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.3596788934354394</v>
+        <v>0.2825289425903295</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>0.1770071023592006</v>
@@ -741,31 +741,31 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.3046189662442481</v>
+        <v>0.2852516046945102</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.2974474138136327</v>
+        <v>0.2719524861913415</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.1627056823757861</v>
+        <v>0.1590181827395362</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.2673855778805653</v>
+        <v>0.2742613939035197</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.1760906830165831</v>
+        <v>0.1600511635163882</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0.1431381799066457</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.2868650431884341</v>
+        <v>0.2800186534508048</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.2375310080122792</v>
+        <v>0.2190223720583206</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.1533860963402506</v>
+        <v>0.1515456261628835</v>
       </c>
     </row>
     <row r="8">
@@ -776,31 +776,31 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.2290617217468384</v>
+        <v>0.214040134472884</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.2168931153297844</v>
+        <v>0.1947535001322798</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.07407674869808918</v>
+        <v>0.07620982963969627</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.1906047583900343</v>
+        <v>0.2035406460106678</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.1118232230109585</v>
+        <v>0.1001402551126636</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0.06232381465888505</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.2302309705778138</v>
+        <v>0.2278863389685884</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.1876455185763573</v>
+        <v>0.1745367328755554</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.08864266051079366</v>
+        <v>0.08405337898825953</v>
       </c>
     </row>
     <row r="9">
@@ -811,31 +811,31 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.3893856052088294</v>
+        <v>0.3715321253373796</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.3871594996767837</v>
+        <v>0.3518714546356553</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.3278973853658317</v>
+        <v>0.3029115351852726</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.3518781957811756</v>
+        <v>0.3636213340789082</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.2568509048451824</v>
+        <v>0.2263231994049044</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>0.2681272002779717</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.3521338498338696</v>
+        <v>0.338726602244893</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.3011415484237331</v>
+        <v>0.2725825682429706</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.2478737955553512</v>
+        <v>0.2494446346082015</v>
       </c>
     </row>
     <row r="10">
@@ -850,31 +850,31 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.1970249320041655</v>
+        <v>0.1944981674788208</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.2185986703454311</v>
+        <v>0.2112310604131865</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.3300068826007778</v>
+        <v>0.3168285283778571</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.187800179339365</v>
+        <v>0.1745401114735619</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.09308456868747475</v>
+        <v>0.09183955964445942</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.1598907149702696</v>
+        <v>0.151037480695843</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.1924893234993134</v>
+        <v>0.1846540567363829</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.157426760354193</v>
+        <v>0.1536639661900095</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.2458480946255779</v>
+        <v>0.2366744246560696</v>
       </c>
     </row>
     <row r="11">
@@ -885,31 +885,31 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.1171125368177026</v>
+        <v>0.12239147884319</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.137431335382515</v>
+        <v>0.1306964605797341</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.1929020757351489</v>
+        <v>0.1783640190802402</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.1127702602953406</v>
+        <v>0.1071407466353957</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.03967327465946137</v>
+        <v>0.04012779706313417</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.06755352800685827</v>
+        <v>0.05783927472996925</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.1344344612505783</v>
+        <v>0.133875852440719</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.1064409601792683</v>
+        <v>0.1073594004864074</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.151777073180903</v>
+        <v>0.1533180529008951</v>
       </c>
     </row>
     <row r="12">
@@ -920,31 +920,31 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.2908438476173356</v>
+        <v>0.2776730591252275</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.3221431807315184</v>
+        <v>0.3003058420361637</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.4918724430221533</v>
+        <v>0.4775580712521358</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.3008937765963516</v>
+        <v>0.2802867286526048</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.169428306873737</v>
+        <v>0.1834607900823142</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.2972371833098587</v>
+        <v>0.2790318380296918</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.257312524439906</v>
+        <v>0.2553795912885298</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.2221952581489592</v>
+        <v>0.2163438162613572</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.3540023493619066</v>
+        <v>0.3391666881656266</v>
       </c>
     </row>
     <row r="13">
@@ -959,31 +959,31 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.2855564316789023</v>
+        <v>0.2568890864579249</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.2799806255792562</v>
+        <v>0.2530517175208696</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.1127109889116028</v>
+        <v>0.08945141328850673</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.1410917888378873</v>
+        <v>0.128179817091444</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.1534183601666187</v>
+        <v>0.1205696112964009</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.04977940207877037</v>
+        <v>0.04845375104911621</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.2164870635828831</v>
+        <v>0.1961538736912365</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.2240952508427552</v>
+        <v>0.1919025173632026</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.07557139750553933</v>
+        <v>0.06731128119643688</v>
       </c>
     </row>
     <row r="14">
@@ -994,31 +994,31 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.1914258942231699</v>
+        <v>0.1746841223840148</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.1787267406720276</v>
+        <v>0.1681564538375045</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.07301137738971153</v>
+        <v>0.07073002932583895</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.07300602698860841</v>
+        <v>0.05981586930725128</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.1472307619108143</v>
+        <v>0.1410371855690013</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.1591408068395039</v>
+        <v>0.1296700472685627</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.01562801935870995</v>
+        <v>0.01330572587794042</v>
       </c>
     </row>
     <row r="15">
@@ -1029,31 +1029,31 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.3966328606683293</v>
+        <v>0.3561969443567023</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.418740221942433</v>
+        <v>0.3709877337311537</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.4144624618068122</v>
+        <v>0.3250250133665699</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.2474488178861273</v>
+        <v>0.2217340665407515</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.2844478327830304</v>
+        <v>0.2129295231298293</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.252759151430381</v>
+        <v>0.2130595726282877</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.2865604235580514</v>
+        <v>0.2617390514660163</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.3207056316469192</v>
+        <v>0.2660611931515268</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.2012127788458629</v>
+        <v>0.1925919836654575</v>
       </c>
     </row>
     <row r="16">
@@ -1068,31 +1068,31 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.2647090735305641</v>
+        <v>0.2022406649355196</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.1378447068998319</v>
+        <v>0.1408079620049003</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.2101792991883896</v>
+        <v>0.1973611954380402</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.1747281168605573</v>
+        <v>0.1791846274709722</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.1021625267236238</v>
+        <v>0.08661099703344929</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.2433352011407437</v>
+        <v>0.2542594238243148</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.2223358795054674</v>
+        <v>0.1905431136958579</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.1208190380981204</v>
+        <v>0.1140064761994657</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.2255374803044445</v>
+        <v>0.2235007198928309</v>
       </c>
     </row>
     <row r="17">
@@ -1103,31 +1103,31 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.1440145712634134</v>
+        <v>0.1094423998120797</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.06128742166301877</v>
+        <v>0.06759777806010174</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.1105381027095039</v>
+        <v>0.1010363289585449</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.0638009147372163</v>
+        <v>0.08553423759038914</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.03949511969915773</v>
+        <v>0.03241757657103625</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.1360309607332048</v>
+        <v>0.1465204410228961</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.1334873112633509</v>
+        <v>0.1185872171321361</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.06695196453900393</v>
+        <v>0.06092439608079302</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.1456391785240413</v>
+        <v>0.1453627939100756</v>
       </c>
     </row>
     <row r="18">
@@ -1138,31 +1138,31 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.4057635635207453</v>
+        <v>0.328272253556563</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.2563735173942316</v>
+        <v>0.2568345460534843</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.35270852759966</v>
+        <v>0.33557021412891</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.3234637675997309</v>
+        <v>0.2996370721040563</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.2143252002382691</v>
+        <v>0.1789819673856843</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.3997571099891547</v>
+        <v>0.3809338711194183</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.3142250994720736</v>
+        <v>0.2717899510079229</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.2099341350904598</v>
+        <v>0.1783317858425113</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.309807134752689</v>
+        <v>0.3141991803454234</v>
       </c>
     </row>
     <row r="19">
@@ -1177,31 +1177,31 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.169734904434926</v>
+        <v>0.1681573859198577</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.2538462770261865</v>
+        <v>0.2696449441356565</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.2250578501291984</v>
+        <v>0.2045955717062595</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.1303812354656226</v>
+        <v>0.1490075922940573</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0903733980401996</v>
+        <v>0.08754008075971381</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.03723243253931485</v>
+        <v>0.06558415315983222</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.1495110764821942</v>
+        <v>0.1587827649650006</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.1744193337806491</v>
+        <v>0.1806896938074185</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.1473540552280381</v>
+        <v>0.1465601664119969</v>
       </c>
     </row>
     <row r="20">
@@ -1212,31 +1212,31 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.09109247468297446</v>
+        <v>0.09107550280826769</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.1597165702218075</v>
+        <v>0.1743186594599799</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.1049841246597333</v>
+        <v>0.0996232070448768</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.0690251849058644</v>
+        <v>0.07775704891677707</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.03185582125985748</v>
+        <v>0.04117651914202325</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0.09994592586986847</v>
+        <v>0.09835036055747834</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.1099738619578328</v>
+        <v>0.1191127290756422</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.07260054792393492</v>
+        <v>0.07557101954516675</v>
       </c>
     </row>
     <row r="21">
@@ -1247,31 +1247,31 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.2867636135633929</v>
+        <v>0.2767163855242713</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.3716692094072016</v>
+        <v>0.3906699947679234</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.3888231557747327</v>
+        <v>0.3516748014816065</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.2301754192080569</v>
+        <v>0.2722298692250062</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.1792868818028767</v>
+        <v>0.1788014232899344</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.1864239681312607</v>
+        <v>0.2027862845953532</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.2249946184100857</v>
+        <v>0.2286646404462042</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.2445153718760544</v>
+        <v>0.2526658811571016</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.2476494368768297</v>
+        <v>0.2443661582758893</v>
       </c>
     </row>
     <row r="22">
@@ -1286,31 +1286,31 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.2520515226137893</v>
+        <v>0.2244606850860137</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.1462399623030922</v>
+        <v>0.1281338621610912</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.2925505081757082</v>
+        <v>0.2822043863436539</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.1600709256683901</v>
+        <v>0.1664908864271637</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.1189399125590925</v>
+        <v>0.1200006514008388</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0.1842662605383772</v>
+        <v>0.1887749248091128</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.2062216865557513</v>
+        <v>0.19590977466719</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.1333680779881395</v>
+        <v>0.1242582580607799</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.2475691578578189</v>
+        <v>0.2426734141572358</v>
       </c>
     </row>
     <row r="23">
@@ -1321,31 +1321,31 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.1887084033229975</v>
+        <v>0.1653123083683194</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.09733557589124103</v>
+        <v>0.08626884887375279</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.1992240473847112</v>
+        <v>0.1946565202261635</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.1052049054538536</v>
+        <v>0.1150833448559026</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.07564616332003871</v>
+        <v>0.07938459445498369</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0.1054030477528372</v>
+        <v>0.1052245641092876</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.1638712453620685</v>
+        <v>0.1568450441758293</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.09532381407547431</v>
+        <v>0.09199398038755642</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.1724855065270693</v>
+        <v>0.1778513635547236</v>
       </c>
     </row>
     <row r="24">
@@ -1356,31 +1356,31 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.3332509273889395</v>
+        <v>0.2913174969590346</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.2079600042078818</v>
+        <v>0.1843504718980286</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.4047737442402341</v>
+        <v>0.3910799567165425</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.2310774710076076</v>
+        <v>0.2308068456182186</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.1792566133359111</v>
+        <v>0.174883190822641</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0.3012383263622803</v>
+        <v>0.2930839045998028</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.2553571989948036</v>
+        <v>0.2426251337621846</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.1790006172420918</v>
+        <v>0.1616928959291239</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.3220795348448657</v>
+        <v>0.3197322971934743</v>
       </c>
     </row>
     <row r="25">
@@ -1395,31 +1395,31 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0.3657297428628707</v>
+        <v>0.3409128218265909</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0.1846581417907723</v>
+        <v>0.1722311943082714</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.1418420857842079</v>
+        <v>0.1384666229043152</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.32792523079734</v>
+        <v>0.2902635608199216</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.1523663179239034</v>
+        <v>0.1447383103348938</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>0.04269371870690678</v>
+        <v>0.03928013974695185</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>0.3470798426025192</v>
+        <v>0.3155866771496097</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>0.1689684111608936</v>
+        <v>0.159092014518124</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.1025582512198531</v>
+        <v>0.09775356272138055</v>
       </c>
     </row>
     <row r="26">
@@ -1430,31 +1430,31 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>0.2992052729598035</v>
+        <v>0.2854356544658162</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0.1373771866993054</v>
+        <v>0.1243397185808623</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.07686892393518439</v>
+        <v>0.07806340263653903</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.2560417494644416</v>
+        <v>0.2357633942887888</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.1029677576615315</v>
+        <v>0.1029961146892973</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>0.01581094702211937</v>
+        <v>0.01433522837356777</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>0.2993283487211726</v>
+        <v>0.272470647186592</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>0.133125069865792</v>
+        <v>0.1247371280295362</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>0.065030427562939</v>
+        <v>0.05981054236089425</v>
       </c>
     </row>
     <row r="27">
@@ -1465,31 +1465,31 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>0.4357656331722011</v>
+        <v>0.4083459155977427</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0.2440928973062571</v>
+        <v>0.2270220766236936</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.2247623733226667</v>
+        <v>0.2123836151674946</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.3990714038891077</v>
+        <v>0.3566401161053993</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.2115912559886879</v>
+        <v>0.2000812896676857</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>0.0964385069743081</v>
+        <v>0.08127689751330727</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>0.3957762332035195</v>
+        <v>0.3610831194824085</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>0.2126430260340582</v>
+        <v>0.1969274307974091</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>0.1621591326013449</v>
+        <v>0.1509272279698203</v>
       </c>
     </row>
     <row r="28">
@@ -1504,31 +1504,31 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>0.2807150773981362</v>
+        <v>0.2584946618186473</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0.2147325958129284</v>
+        <v>0.2026631501550434</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.199577453218781</v>
+        <v>0.1916390354652999</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.218121588944378</v>
+        <v>0.2102289689071407</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.1391908963230728</v>
+        <v>0.128250271495198</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0.1170031953429169</v>
+        <v>0.1187915259234743</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0.2501080246998801</v>
+        <v>0.2349478947396191</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0.1783443098308589</v>
+        <v>0.167118795285524</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0.16288063728964</v>
+        <v>0.1592113937317494</v>
       </c>
     </row>
     <row r="29">
@@ -1539,31 +1539,31 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>0.2507700043450333</v>
+        <v>0.2308892092994714</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0.1870940664698035</v>
+        <v>0.176747335080706</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.1610977255455545</v>
+        <v>0.1558067116395825</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.1890184602461841</v>
+        <v>0.1842705667851912</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.1175470932371663</v>
+        <v>0.10599752830818</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.0877790334129884</v>
+        <v>0.08870829937120299</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>0.2285624377737537</v>
+        <v>0.214265771825843</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>0.159939460990371</v>
+        <v>0.1504129073899769</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>0.1398170843121347</v>
+        <v>0.136264711853671</v>
       </c>
     </row>
     <row r="30">
@@ -1574,31 +1574,31 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>0.3141416914663673</v>
+        <v>0.2887002357744994</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>0.2481324942288383</v>
+        <v>0.2290646092616782</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.2475552608383892</v>
+        <v>0.2365777460481445</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.2487304796293391</v>
+        <v>0.2393603117884866</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.1691366455307075</v>
+        <v>0.1502560382600164</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0.153483405076763</v>
+        <v>0.1557822107223183</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>0.2729750716981049</v>
+        <v>0.2553922250896048</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>0.1994719594363856</v>
+        <v>0.1855186742623794</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0.1967909768119987</v>
+        <v>0.1891680988468435</v>
       </c>
     </row>
     <row r="31">
@@ -1653,7 +1653,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 71,23%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1753,28 +1753,28 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>6</v>
@@ -1788,28 +1788,28 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>10125</v>
+        <v>14247</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>8304</v>
+        <v>13343</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>2845</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>6976</v>
+        <v>9073</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>7156</v>
+        <v>8118</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>1262</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>17101</v>
+        <v>23321</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>15460</v>
+        <v>21461</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>4106</v>
@@ -1823,28 +1823,28 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>6128</v>
+        <v>9592</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>5004</v>
+        <v>8491</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>730</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>3362</v>
+        <v>5404</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>3781</v>
+        <v>4419</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>12068</v>
+        <v>16631</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>10205</v>
+        <v>15329</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>1903</v>
@@ -1858,28 +1858,28 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>15142</v>
+        <v>21461</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>12069</v>
+        <v>18686</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>6513</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>11084</v>
+        <v>14037</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>11545</v>
+        <v>12914</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>4405</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>23195</v>
+        <v>30233</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>21002</v>
+        <v>28815</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>8973</v>
@@ -1897,28 +1897,28 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>9</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>7</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>16</v>
@@ -1932,28 +1932,28 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>24758</v>
+        <v>27168</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>23588</v>
+        <v>26917</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>6818</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>19807</v>
+        <v>23743</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>13618</v>
+        <v>14219</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>5454</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>44565</v>
+        <v>50911</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>37206</v>
+        <v>41136</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>12272</v>
@@ -1967,31 +1967,31 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>18617</v>
+        <v>20386</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>17200</v>
+        <v>19276</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>3104</v>
+        <v>3267</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>14119</v>
+        <v>17620</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>8648</v>
+        <v>8896</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>2375</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>35767</v>
+        <v>41433</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>29392</v>
+        <v>32781</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>7092</v>
+        <v>6807</v>
       </c>
     </row>
     <row r="11">
@@ -2002,31 +2002,31 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>31647</v>
+        <v>35386</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>30703</v>
+        <v>34828</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>13740</v>
+        <v>12987</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>26066</v>
+        <v>31478</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>19864</v>
+        <v>20106</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>10217</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>54704</v>
+        <v>61585</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>47170</v>
+        <v>51195</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>19832</v>
+        <v>20200</v>
       </c>
     </row>
     <row r="12">
@@ -2041,16 +2041,16 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>7</v>
@@ -2059,13 +2059,13 @@
         <v>6</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>25</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -2076,16 +2076,16 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>10367</v>
+        <v>11715</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>12875</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>7209</v>
+        <v>7664</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>9558</v>
+        <v>10233</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>5212</v>
@@ -2094,13 +2094,13 @@
         <v>3420</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>19925</v>
+        <v>21948</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>18088</v>
+        <v>18087</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>10629</v>
+        <v>11084</v>
       </c>
     </row>
     <row r="14">
@@ -2111,31 +2111,31 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>6162</v>
+        <v>7372</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>8094</v>
+        <v>7966</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4214</v>
+        <v>4315</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>5739</v>
+        <v>6281</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>2222</v>
+        <v>2277</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>1445</v>
+        <v>1310</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>13915</v>
+        <v>15912</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>12230</v>
+        <v>12637</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>6562</v>
+        <v>7180</v>
       </c>
     </row>
     <row r="15">
@@ -2146,31 +2146,31 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>15303</v>
+        <v>16725</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>18974</v>
+        <v>18305</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>10745</v>
+        <v>11552</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>15314</v>
+        <v>16432</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>9487</v>
+        <v>10412</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>6357</v>
+        <v>6318</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>26634</v>
+        <v>30354</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>25529</v>
+        <v>25465</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>15304</v>
+        <v>15884</v>
       </c>
     </row>
     <row r="16">
@@ -2185,28 +2185,28 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>3</v>
@@ -2220,28 +2220,28 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>16061</v>
+        <v>17807</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>12244</v>
+        <v>14841</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>1336</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>7270</v>
+        <v>7939</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>5305</v>
+        <v>6062</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>850</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>23331</v>
+        <v>25746</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>17549</v>
+        <v>20903</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>2186</v>
@@ -2255,31 +2255,31 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>10767</v>
+        <v>12109</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>7816</v>
+        <v>9862</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>3762</v>
+        <v>4381</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>2524</v>
+        <v>3007</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>15867</v>
+        <v>18511</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>12462</v>
+        <v>14124</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>452</v>
+        <v>432</v>
       </c>
     </row>
     <row r="19">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>22308</v>
+        <v>24691</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>18312</v>
+        <v>21758</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>4914</v>
+        <v>4856</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>12750</v>
+        <v>13733</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>9836</v>
+        <v>10705</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>4316</v>
+        <v>3737</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>30882</v>
+        <v>34354</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>25114</v>
+        <v>28980</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>5821</v>
+        <v>6256</v>
       </c>
     </row>
     <row r="20">
@@ -2332,28 +2332,28 @@
         <v>11</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>5</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -2367,28 +2367,28 @@
         <v>7953</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>4836</v>
+        <v>5436</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>5285</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>4672</v>
+        <v>7256</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>3271</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>5280</v>
+        <v>5786</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>12625</v>
+        <v>15209</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>8108</v>
+        <v>8707</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>10564</v>
+        <v>11070</v>
       </c>
     </row>
     <row r="22">
@@ -2399,31 +2399,31 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>4327</v>
+        <v>4304</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2150</v>
+        <v>2610</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>2779</v>
+        <v>2705</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1706</v>
+        <v>3464</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>1265</v>
+        <v>1224</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>2951</v>
+        <v>3334</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>7580</v>
+        <v>9466</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>4493</v>
+        <v>4653</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>6822</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="23">
@@ -2434,31 +2434,31 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>12190</v>
+        <v>12909</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>8995</v>
+        <v>9915</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>8868</v>
+        <v>8985</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>8649</v>
+        <v>12134</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>6862</v>
+        <v>6760</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>8674</v>
+        <v>8668</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>17843</v>
+        <v>21694</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>14088</v>
+        <v>13620</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>14511</v>
+        <v>15563</v>
       </c>
     </row>
     <row r="24">
@@ -2473,31 +2473,31 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>9</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>7</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -2508,31 +2508,31 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>7073</v>
+        <v>8201</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>12318</v>
+        <v>13368</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>5037</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>5744</v>
+        <v>6969</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>4144</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>588</v>
+        <v>1157</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>12817</v>
+        <v>15170</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>16463</v>
+        <v>17512</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>5625</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="26">
@@ -2543,31 +2543,31 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>3796</v>
+        <v>4442</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>7750</v>
+        <v>8642</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>2350</v>
+        <v>2453</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>3041</v>
+        <v>3637</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>1461</v>
+        <v>1949</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>8568</v>
+        <v>9396</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>10380</v>
+        <v>11544</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>2772</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="27">
@@ -2578,31 +2578,31 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>11950</v>
+        <v>13495</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>18036</v>
+        <v>19368</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>8703</v>
+        <v>8659</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>10140</v>
+        <v>12732</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>8222</v>
+        <v>8465</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>2944</v>
+        <v>3578</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>19288</v>
+        <v>21846</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>23079</v>
+        <v>24488</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>9454</v>
+        <v>10329</v>
       </c>
     </row>
     <row r="28">
@@ -2620,28 +2620,28 @@
         <v>37</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J28" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="K28" s="6" t="n">
         <v>39</v>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>38</v>
       </c>
     </row>
     <row r="29">
@@ -2655,28 +2655,28 @@
         <v>26426</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>15468</v>
+        <v>16120</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>19112</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>16665</v>
+        <v>19023</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>11223</v>
+        <v>13743</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>8554</v>
+        <v>9377</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>43091</v>
+        <v>45448</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>26691</v>
+        <v>29863</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>27666</v>
+        <v>28489</v>
       </c>
     </row>
     <row r="30">
@@ -2687,31 +2687,31 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>19785</v>
+        <v>19462</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>10295</v>
+        <v>10853</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>13015</v>
+        <v>13183</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>10953</v>
+        <v>13149</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>7138</v>
+        <v>9091</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>4893</v>
+        <v>5227</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>34242</v>
+        <v>36386</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>19077</v>
+        <v>22109</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>19276</v>
+        <v>20879</v>
       </c>
     </row>
     <row r="31">
@@ -2722,31 +2722,31 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>34939</v>
+        <v>34297</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>21996</v>
+        <v>23193</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>26444</v>
+        <v>26486</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>24058</v>
+        <v>26371</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>16915</v>
+        <v>20028</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>13984</v>
+        <v>14558</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>53358</v>
+        <v>56286</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>35824</v>
+        <v>38859</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>35993</v>
+        <v>37536</v>
       </c>
     </row>
     <row r="32">
@@ -2761,28 +2761,28 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H32" s="6" t="n">
         <v>5</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>19</v>
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>44117</v>
+        <v>48266</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>22934</v>
+        <v>25082</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>11296</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>38515</v>
+        <v>41100</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>17883</v>
+        <v>19294</v>
       </c>
       <c r="H33" s="6" t="n">
         <v>2231</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>82632</v>
+        <v>89366</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>40817</v>
+        <v>44376</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>13527</v>
@@ -2831,31 +2831,31 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>36093</v>
+        <v>40412</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>17062</v>
+        <v>18107</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>6122</v>
+        <v>6368</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>30072</v>
+        <v>33383</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>12085</v>
+        <v>13730</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>71263</v>
+        <v>77157</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>32158</v>
+        <v>34793</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>8577</v>
+        <v>8277</v>
       </c>
     </row>
     <row r="35">
@@ -2866,31 +2866,31 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>52566</v>
+        <v>57813</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>30315</v>
+        <v>33061</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>17900</v>
+        <v>17326</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>46871</v>
+        <v>50499</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>24834</v>
+        <v>26672</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>5040</v>
+        <v>4617</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>94226</v>
+        <v>102250</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>51367</v>
+        <v>54930</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>21389</v>
+        <v>20886</v>
       </c>
     </row>
     <row r="36">
@@ -2905,31 +2905,31 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="37">
@@ -2940,31 +2940,31 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>146880</v>
+        <v>161783</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>112567</v>
+        <v>127982</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>58938</v>
+        <v>59393</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>109207</v>
+        <v>125336</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>67814</v>
+        <v>74064</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>27638</v>
+        <v>29537</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>256087</v>
+        <v>287119</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>180381</v>
+        <v>202045</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>86577</v>
+        <v>88930</v>
       </c>
     </row>
     <row r="38">
@@ -2975,31 +2975,31 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>131211</v>
+        <v>144506</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>98079</v>
+        <v>111616</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>47575</v>
+        <v>48288</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>94636</v>
+        <v>109860</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>57269</v>
+        <v>61213</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>20735</v>
+        <v>22057</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>234026</v>
+        <v>261844</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>161766</v>
+        <v>181848</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>74318</v>
+        <v>76113</v>
       </c>
     </row>
     <row r="39">
@@ -3010,31 +3010,31 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>164370</v>
+        <v>180688</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>130076</v>
+        <v>144654</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>73107</v>
+        <v>73321</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>124532</v>
+        <v>142704</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>82403</v>
+        <v>86772</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>36256</v>
+        <v>38734</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>279500</v>
+        <v>312103</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>201750</v>
+        <v>224291</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>104601</v>
+        <v>105663</v>
       </c>
     </row>
     <row r="40">
